--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488145_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488145_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3151</v>
+        <v>6.1719</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7706</v>
+        <v>4.652</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5445</v>
+        <v>1.5199</v>
       </c>
       <c r="G2" t="n">
         <v>4.1205</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0463</v>
+        <v>0.8105</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3954</v>
+        <v>0.4859</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3492</v>
+        <v>0.3245</v>
       </c>
       <c r="V2" t="n">
         <v>0.3144</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1444</v>
+        <v>3.3396</v>
       </c>
       <c r="E3" t="n">
-        <v>1.196</v>
+        <v>0.859</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9485</v>
+        <v>2.4807</v>
       </c>
       <c r="G3" t="n">
         <v>0.8829</v>
@@ -688,13 +688,13 @@
         <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4289</v>
+        <v>1.624</v>
       </c>
       <c r="T3" t="n">
-        <v>1.399</v>
+        <v>1.062</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0299</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>1.5738</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.499</v>
+        <v>2.0612</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.8128</v>
+        <v>-2.7581</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3118</v>
+        <v>4.8193</v>
       </c>
       <c r="G4" t="n">
         <v>3.1417</v>
@@ -766,13 +766,13 @@
         <v>2.2234</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1192</v>
+        <v>0.6814</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2226</v>
+        <v>-0.1679</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3417</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>1.5733</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3668</v>
+        <v>1.9018</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3477</v>
+        <v>-0.2777</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0191</v>
+        <v>2.1795</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1613</v>
+        <v>1.3549</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9092</v>
+        <v>1.9232</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2521</v>
+        <v>-0.5683</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9113</v>
+        <v>0.1329</v>
       </c>
       <c r="K5" t="n">
-        <v>2.237</v>
+        <v>1.4386</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6742</v>
+        <v>-1.3057</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.75</v>
+        <v>1.222</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3278</v>
+        <v>0.4846</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4221</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1117</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2628</v>
+        <v>0.2145</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1613</v>
+        <v>0.1834</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1015</v>
+        <v>0.0311</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9455</v>
+        <v>1.2589</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.9455</v>
+        <v>1.2589</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0484</v>
+        <v>1.7875</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0819</v>
+        <v>0.3252</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1303</v>
+        <v>1.4623</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3549</v>
+        <v>2.1613</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9232</v>
+        <v>1.9092</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5683</v>
+        <v>0.2521</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1329</v>
+        <v>2.9113</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4386</v>
+        <v>2.237</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3057</v>
+        <v>0.6742</v>
       </c>
       <c r="M6" t="n">
-        <v>1.222</v>
+        <v>-0.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4846</v>
+        <v>-0.3278</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7374000000000001</v>
+        <v>-0.4221</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3611</v>
+        <v>1.6834</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3793</v>
+        <v>1.1388</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0182</v>
+        <v>0.5446</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2589</v>
+        <v>-0.9455</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2589</v>
+        <v>-0.9455</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>U. CHAGOYEN SALGUERO</t>
+          <t>R. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8354</v>
+        <v>1.6913</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9239000000000001</v>
+        <v>1.095</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9115</v>
+        <v>0.5962</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6996</v>
+        <v>1.4026</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0052</v>
+        <v>1.1415</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6943</v>
+        <v>0.2611</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5138</v>
+        <v>1.095</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4724</v>
+        <v>1.095</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1857</v>
+        <v>0.3076</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4671</v>
+        <v>0.0464</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6529</v>
+        <v>0.2611</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3947</v>
+        <v>0.0473</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2189</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6135</v>
+        <v>0.0473</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. ORTEGA MORA</t>
+          <t>U. CHAGOYEN SALGUERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6174</v>
+        <v>1.6384</v>
       </c>
       <c r="E8" t="n">
-        <v>1.095</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5224</v>
+        <v>0.7146</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4026</v>
+        <v>0.6996</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1415</v>
+        <v>0.0052</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2611</v>
+        <v>0.6943</v>
       </c>
       <c r="J8" t="n">
-        <v>1.095</v>
+        <v>0.5138</v>
       </c>
       <c r="K8" t="n">
-        <v>1.095</v>
+        <v>0.4724</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3076</v>
+        <v>0.1857</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0464</v>
+        <v>-0.4671</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2611</v>
+        <v>0.6529</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0266</v>
+        <v>0.1977</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.2189</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0266</v>
+        <v>0.4166</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3969</v>
+        <v>0.7476</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7323</v>
+        <v>-1.7755</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1292</v>
+        <v>2.5232</v>
       </c>
       <c r="G9" t="n">
         <v>0.4837</v>
@@ -1156,13 +1156,13 @@
         <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6427</v>
+        <v>-0.2919</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0584</v>
+        <v>-0.1016</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.1903</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2913</v>
+        <v>0.1239</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2171</v>
+        <v>0.8047</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5085</v>
+        <v>-0.6808</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2459</v>
@@ -1234,13 +1234,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3987</v>
+        <v>0.8139</v>
       </c>
       <c r="T10" t="n">
-        <v>0.097</v>
+        <v>0.6846</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3017</v>
+        <v>0.1293</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4515</v>
+        <v>-3.7091</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.401</v>
+        <v>-5.0525</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9495</v>
+        <v>1.3435</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4613</v>
@@ -1312,13 +1312,13 @@
         <v>1.8529</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0861</v>
+        <v>0.8285</v>
       </c>
       <c r="T11" t="n">
-        <v>0.148</v>
+        <v>0.4965</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0619</v>
+        <v>0.332</v>
       </c>
       <c r="V11" t="n">
         <v>0.6294</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.4806</v>
+        <v>15.7541</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.477700000000001</v>
+        <v>-1.204</v>
       </c>
       <c r="F12" t="n">
-        <v>16.9583</v>
+        <v>16.9584</v>
       </c>
       <c r="G12" t="n">
         <v>11.54</v>
@@ -1372,13 +1372,13 @@
         <v>-4.9931</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3281000000000001</v>
+        <v>0.3280999999999996</v>
       </c>
       <c r="N12" t="n">
         <v>-1.3634</v>
       </c>
       <c r="O12" t="n">
-        <v>1.691600000000001</v>
+        <v>1.6916</v>
       </c>
       <c r="P12" t="n">
         <v>-6.4849</v>
@@ -1390,19 +1390,19 @@
         <v>13.8966</v>
       </c>
       <c r="S12" t="n">
-        <v>6.3359</v>
+        <v>6.6093</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2893</v>
+        <v>3.562800000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0466</v>
+        <v>3.0464</v>
       </c>
       <c r="V12" t="n">
         <v>4.0899</v>
       </c>
       <c r="W12" t="n">
-        <v>4.4027</v>
+        <v>4.402699999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-0.3128</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4639</v>
+        <v>3.5956</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1873</v>
+        <v>1.9914</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2766</v>
+        <v>1.6042</v>
       </c>
       <c r="G13" t="n">
         <v>1.3772</v>
@@ -1468,13 +1468,13 @@
         <v>2.2234</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0811</v>
+        <v>-0.9494</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2226</v>
+        <v>-0.4184</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8585</v>
+        <v>-0.531</v>
       </c>
       <c r="V13" t="n">
         <v>0.9444</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0841</v>
+        <v>3.2474</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6777</v>
+        <v>2.5797</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4065</v>
+        <v>0.6676</v>
       </c>
       <c r="G14" t="n">
         <v>3.024</v>
@@ -1546,13 +1546,13 @@
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3306</v>
+        <v>-1.1674</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4414</v>
+        <v>-0.5394</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8891</v>
+        <v>-0.628</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5738</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.684</v>
+        <v>3.035</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3916</v>
+        <v>1.5874</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2924</v>
+        <v>1.4476</v>
       </c>
       <c r="G15" t="n">
         <v>2.0573</v>
@@ -1624,13 +1624,13 @@
         <v>1.4823</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1712</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6019</v>
+        <v>-0.406</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5693</v>
+        <v>-0.4141</v>
       </c>
       <c r="V15" t="n">
         <v>0.3155</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0859</v>
+        <v>2.2079</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9106</v>
+        <v>2.1064</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1753</v>
+        <v>0.1014</v>
       </c>
       <c r="G16" t="n">
         <v>0.209</v>
@@ -1702,13 +1702,13 @@
         <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0055</v>
+        <v>0.1275</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2313</v>
+        <v>-0.0354</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2368</v>
+        <v>0.1629</v>
       </c>
       <c r="V16" t="n">
         <v>0.945</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1999</v>
+        <v>-1.2439</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5189</v>
+        <v>-0.7542</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7187</v>
+        <v>-0.4897</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1657</v>
@@ -1858,13 +1858,13 @@
         <v>2.0382</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7805</v>
+        <v>0.7365</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7783</v>
+        <v>0.5052</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0022</v>
+        <v>0.2313</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.269</v>
+        <v>-1.2455</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7081</v>
+        <v>-2.5123</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4391</v>
+        <v>1.2668</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7224</v>
@@ -1936,13 +1936,13 @@
         <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0289</v>
+        <v>-1.0054</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8754</v>
+        <v>-0.6796</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1535</v>
+        <v>-0.3258</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>J. PONCE GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.694</v>
+        <v>-3.5261</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4161</v>
+        <v>-4.4417</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2779</v>
+        <v>0.9157</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.3085</v>
+        <v>-1.4155</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2824</v>
+        <v>-2.0113</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0261</v>
+        <v>0.5958</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4924</v>
+        <v>-1.1893</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2281</v>
+        <v>-0.6099</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2643</v>
+        <v>-0.5793</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8161</v>
+        <v>-0.2263</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0543</v>
+        <v>-1.4014</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2381</v>
+        <v>1.1751</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0382</v>
+        <v>-1.297</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0227</v>
+        <v>-1.1285</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8556</v>
+        <v>-0.4731</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1671</v>
+        <v>-0.6554</v>
       </c>
       <c r="V20" t="n">
-        <v>0.63</v>
+        <v>0.315</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.63</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PONCE GONZALEZ</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9338</v>
+        <v>-3.8665</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.6376</v>
+        <v>-1.337</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7038</v>
+        <v>-2.5294</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4155</v>
+        <v>-1.4115</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0113</v>
+        <v>-0.4207</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5958</v>
+        <v>-0.9908</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1893</v>
+        <v>-0.0248</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6099</v>
+        <v>1.0736</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5793</v>
+        <v>-1.0984</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2263</v>
+        <v>-1.3867</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4014</v>
+        <v>-1.4943</v>
       </c>
       <c r="O21" t="n">
-        <v>1.1751</v>
+        <v>0.1076</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.297</v>
+        <v>1.8529</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4823</v>
+        <v>2.7793</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5363</v>
+        <v>-0.5313</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.669</v>
+        <v>-0.3858</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8673</v>
+        <v>-0.1455</v>
       </c>
       <c r="V21" t="n">
-        <v>0.315</v>
+        <v>-3.7766</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.315</v>
+        <v>-3.7766</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.377</v>
+        <v>-3.8862</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6269</v>
+        <v>-4.3331</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2499</v>
+        <v>0.4469</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5017</v>
@@ -2170,13 +2170,13 @@
         <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.06</v>
+        <v>-0.5692</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.669</v>
+        <v>-0.3752</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.391</v>
+        <v>-0.194</v>
       </c>
       <c r="V22" t="n">
         <v>-0.63</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.765</v>
+        <v>-4.348</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8267</v>
+        <v>-4.0037</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9383</v>
+        <v>-0.3443</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4115</v>
+        <v>-3.3085</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4207</v>
+        <v>-2.2824</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9908</v>
+        <v>-1.0261</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0248</v>
+        <v>-1.4924</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0736</v>
+        <v>-0.2281</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.0984</v>
+        <v>-1.2643</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3867</v>
+        <v>-1.8161</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4943</v>
+        <v>-2.0543</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1076</v>
+        <v>0.2381</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8529</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7793</v>
+        <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4298</v>
+        <v>0.3687</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8754</v>
+        <v>0.268</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5544</v>
+        <v>0.1007</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.7766</v>
+        <v>0.63</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.7766</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.882</v>
+        <v>-8.466799999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.750999999999999</v>
+        <v>-8.163399999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.131</v>
+        <v>-0.3033</v>
       </c>
       <c r="G24" t="n">
         <v>-6.0042</v>
@@ -2326,13 +2326,13 @@
         <v>2.594</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.0914</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0943</v>
+        <v>-0.5067</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5877</v>
+        <v>0.4153</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2594</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-15.4807</v>
+        <v>-14.175</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.9582</v>
+        <v>-16.9584</v>
       </c>
       <c r="F25" t="n">
-        <v>1.477700000000001</v>
+        <v>2.7835</v>
       </c>
       <c r="G25" t="n">
         <v>-11.5399</v>
@@ -2377,13 +2377,13 @@
         <v>3.301299999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3281000000000005</v>
+        <v>-0.3281000000000009</v>
       </c>
       <c r="K25" t="n">
-        <v>1.3638</v>
+        <v>1.363800000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.6916</v>
+        <v>-1.691600000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-11.2119</v>
@@ -2395,7 +2395,7 @@
         <v>4.992699999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>6.485000000000001</v>
+        <v>6.485</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.8965</v>
@@ -2404,13 +2404,13 @@
         <v>20.3815</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.3358</v>
+        <v>-5.030000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>-3.0464</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.2893</v>
+        <v>-1.9836</v>
       </c>
       <c r="V25" t="n">
         <v>-4.0899</v>
